--- a/data/office/fy26-budget.xlsx
+++ b/data/office/fy26-budget.xlsx
@@ -557,10 +557,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -708,17 +708,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Shared engineering tools and EDA licences</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>860000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Priya Raman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Seat count true-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>R&amp;D total</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>11400000</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>11905000</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>505k over plan</t>
         </is>
